--- a/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1248,7 +1248,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.composed[1]</t>
+          <t xml:space="preserve">ahead.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1273,14 +1273,14 @@
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに拳を握る）</t>
+          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.composed[1]</t>
+          <t xml:space="preserve">behind.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1305,14 +1305,14 @@
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに背を向ける）</t>
+          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
@@ -1337,14 +1337,14 @@
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたけど…悪くない</t>
+          <t xml:space="preserve">………（静かに拳を握る）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
@@ -1369,14 +1369,14 @@
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…これからも</t>
+          <t xml:space="preserve">………（静かに背を向ける）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">loser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1401,14 +1401,14 @@
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに相手を見据える）</t>
+          <t xml:space="preserve">…負けたけど…悪くない</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.composed[1]</t>
+          <t xml:space="preserve">winner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1433,14 +1433,14 @@
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに構える）…来なよ</t>
+          <t xml:space="preserve">……ありがとう。…これからも</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
@@ -1465,14 +1465,14 @@
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに、真っ直ぐ見据えている）</t>
+          <t xml:space="preserve">………（静かに相手を見据える）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに頷く）</t>
+          <t xml:space="preserve">………（静かに構える）…来なよ</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
@@ -1529,14 +1529,14 @@
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今日だ</t>
+          <t xml:space="preserve">………（静かに、真っ直ぐ見据えている）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
@@ -1561,14 +1561,14 @@
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに頷く）…来なよ</t>
+          <t xml:space="preserve">………（静かに頷く）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.quiet.composed[1]</t>
+          <t xml:space="preserve">attacker.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1593,14 +1593,14 @@
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに息を吸い、前を見る）</t>
+          <t xml:space="preserve">……今日だ</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.quiet.composed[1]</t>
+          <t xml:space="preserve">defender.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1625,14 +1625,14 @@
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに微笑み、構える）</t>
+          <t xml:space="preserve">……（静かに頷く）…来なよ</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1657,14 +1657,14 @@
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次だ</t>
+          <t xml:space="preserve">………（静かに息を吸い、前を見る）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">fateDefender.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1689,14 +1689,14 @@
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（一瞬振り返り、前を向く）</t>
+          <t xml:space="preserve">………（静かに微笑み、構える）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.quiet.composed[1]</t>
+          <t xml:space="preserve">loserLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="F45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに立ち上がり、前を見る）</t>
+          <t xml:space="preserve">……次だ</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.quiet.composed[1]</t>
+          <t xml:space="preserve">winnerLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1753,14 +1753,14 @@
       </c>
       <c r="F46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに息を吐く）…一つ、か</t>
+          <t xml:space="preserve">………（一瞬振り返り、前を向く）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.composed[1]</t>
+          <t xml:space="preserve">fateLoser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1785,14 +1785,14 @@
       </c>
       <c r="F47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…負けたか。…次だ</t>
+          <t xml:space="preserve">………（静かに立ち上がり、前を見る）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.composed[1]</t>
+          <t xml:space="preserve">fateWinner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1817,14 +1817,14 @@
       </c>
       <c r="F48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つ、終わったか</t>
+          <t xml:space="preserve">………（静かに息を吐く）…一つ、か</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">loser.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1849,14 +1849,14 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かに天を仰ぐ）</t>
+          <t xml:space="preserve">…負けたか。…次だ</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">winner.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1881,14 +1881,14 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った、か</t>
+          <t xml:space="preserve">…一つ、終わったか</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.quiet.composed[1]</t>
+          <t xml:space="preserve">loserLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1913,14 +1913,14 @@
       </c>
       <c r="F51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{nameB}が静かに{nameA}を見据えた。「…もういい。…覚悟は決めた」</t>
+          <t xml:space="preserve">………（静かに天を仰ぐ）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.lose[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1930,29 +1930,29 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.lose[1]</t>
+          <t xml:space="preserve">winnerLines.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…完敗です。言葉が出ません。</t>
+          <t xml:space="preserve">……勝った、か</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.lose[2]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1962,29 +1962,29 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.lose[2]</t>
+          <t xml:space="preserve">awakening.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">03 因縁・絆(Bond/Rivalry)イベント</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。…情けないです。</t>
+          <t xml:space="preserve">{nameB}が静かに{nameA}を見据えた。「…もういい。…覚悟は決めた」</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.lose[3]</t>
+          <t xml:space="preserve">composed_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…届きませんでした。悔しい。</t>
+          <t xml:space="preserve">…完敗です。言葉が出ません。</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.petition[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.petition[1]</t>
+          <t xml:space="preserve">composed_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2041,14 +2041,14 @@
       </c>
       <c r="F55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人と、やりたいです。</t>
+          <t xml:space="preserve">負けました。…情けないです。</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.petition[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.petition[2]</t>
+          <t xml:space="preserve">composed_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2073,14 +2073,14 @@
       </c>
       <c r="F56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お願いが、ひとつだけ。あの人と、やらせてください。</t>
+          <t xml:space="preserve">…届きませんでした。悔しい。</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.petition[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.petition[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.petition[3]</t>
+          <t xml:space="preserve">composed_quiet.petition[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人です。お願いします。</t>
+          <t xml:space="preserve">社長。…あの人と、やりたいです。</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.sendoff[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.petition[2]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.sendoff[1]</t>
+          <t xml:space="preserve">composed_quiet.petition[2]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2137,14 +2137,14 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。行ってきます。</t>
+          <t xml:space="preserve">…お願いが、ひとつだけ。あの人と、やらせてください。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.sendoff[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.petition[3]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.sendoff[2]</t>
+          <t xml:space="preserve">composed_quiet.petition[3]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="2">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝します。…では、行ってきます。</t>
+          <t xml:space="preserve">社長。…あの人です。お願いします。</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.sendoff[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.sendoff[3]</t>
+          <t xml:space="preserve">composed_quiet.sendoff[1]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="2">
@@ -2201,14 +2201,14 @@
       </c>
       <c r="F60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい。必ず、報告します。</t>
+          <t xml:space="preserve">…ありがとうございます。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.sendoff[2]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.win[1]</t>
+          <t xml:space="preserve">composed_quiet.sendoff[2]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="2">
@@ -2233,14 +2233,14 @@
       </c>
       <c r="F61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。…ありがとうございます。</t>
+          <t xml:space="preserve">感謝します。…では、行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.sendoff[3]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.win[2]</t>
+          <t xml:space="preserve">composed_quiet.sendoff[3]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="2">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝ちました。それだけ、報告に。</t>
+          <t xml:space="preserve">…はい。必ず、報告します。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.win[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.win[3]</t>
+          <t xml:space="preserve">composed_quiet.win[1]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="2">
@@ -2297,14 +2297,14 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わりました。…勝ちです。</t>
+          <t xml:space="preserve">勝てました。…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet._accept[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.win[2]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet._accept[1]</t>
+          <t xml:space="preserve">composed_quiet.win[2]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="2">
@@ -2329,14 +2329,14 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。受けよう。</t>
+          <t xml:space="preserve">…勝ちました。それだけ、報告に。</t>
         </is>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet._accept[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.composed_quiet.win[3]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet._accept[2]</t>
+          <t xml:space="preserve">composed_quiet.win[3]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="F65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…名指しだね。逃げないよ。</t>
+          <t xml:space="preserve">終わりました。…勝ちです。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet._accept[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet._accept[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet._accept[3]</t>
+          <t xml:space="preserve">composed_quiet._accept[1]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="2">
@@ -2393,14 +2393,14 @@
       </c>
       <c r="F66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…来なよ。ちゃんと立ってる。</t>
+          <t xml:space="preserve">…わかった。受けよう。</t>
         </is>
       </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.draw[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet._accept[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.draw[1]</t>
+          <t xml:space="preserve">composed_quiet._accept[2]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="2">
@@ -2425,14 +2425,14 @@
       </c>
       <c r="F67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…決まらなかったね。</t>
+          <t xml:space="preserve">…名指しだね。逃げないよ。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.draw[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet._accept[3]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.draw[2]</t>
+          <t xml:space="preserve">composed_quiet._accept[3]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="2">
@@ -2457,14 +2457,14 @@
       </c>
       <c r="F68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ終わってない。それでいい。</t>
+          <t xml:space="preserve">…来なよ。ちゃんと立ってる。</t>
         </is>
       </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.draw[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.draw[1]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.draw[3]</t>
+          <t xml:space="preserve">composed_quiet.draw[1]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="2">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="F69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…続きは、いつか。</t>
+          <t xml:space="preserve">…決まらなかったね。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.lose[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.draw[2]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.lose[1]</t>
+          <t xml:space="preserve">composed_quiet.draw[2]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="2">
@@ -2521,14 +2521,14 @@
       </c>
       <c r="F70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…強かった。それが答えだ。</t>
+          <t xml:space="preserve">…まだ終わってない。それでいい。</t>
         </is>
       </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.lose[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.draw[3]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.lose[2]</t>
+          <t xml:space="preserve">composed_quiet.draw[3]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="2">
@@ -2553,14 +2553,14 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めるよ。今日は。</t>
+          <t xml:space="preserve">…続きは、いつか。</t>
         </is>
       </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.lose[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.lose[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.lose[3]</t>
+          <t xml:space="preserve">composed_quiet.lose[1]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="2">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="F72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…立てない。参った。</t>
+          <t xml:space="preserve">…強かった。それが答えだ。</t>
         </is>
       </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.win[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.lose[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.win[1]</t>
+          <t xml:space="preserve">composed_quiet.lose[2]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="2">
@@ -2617,14 +2617,14 @@
       </c>
       <c r="F73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。届かなかったね、今日は。</t>
+          <t xml:space="preserve">…認めるよ。今日は。</t>
         </is>
       </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.win[2]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.lose[3]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.win[2]</t>
+          <t xml:space="preserve">composed_quiet.lose[3]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr" s="2">
@@ -2649,14 +2649,14 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…想定の内。それだけ。</t>
+          <t xml:space="preserve">…立てない。参った。</t>
         </is>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.win[3]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.win[1]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed_quiet.win[3]</t>
+          <t xml:space="preserve">composed_quiet.win[1]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr" s="2">
@@ -2681,14 +2681,14 @@
       </c>
       <c r="F75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい目してた。また来なよ。</t>
+          <t xml:space="preserve">…うん。届かなかったね、今日は。</t>
         </is>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.quiet.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.win[2]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2698,29 +2698,29 @@
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.quiet.composed[1]</t>
+          <t xml:space="preserve">composed_quiet.win[2]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少しだけ</t>
+          <t xml:space="preserve">…想定の内。それだけ。</t>
         </is>
       </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.composed_quiet.win[3]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2730,29 +2730,29 @@
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">composed_quiet.win[3]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう一度だけ</t>
+          <t xml:space="preserve">…いい目してた。また来なよ。</t>
         </is>
       </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.quiet.composed[1]</t>
+          <t xml:space="preserve">accepted.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……いいよ</t>
+          <t xml:space="preserve">…じゃあね…</t>
         </is>
       </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.quiet.composed[1]</t>
+          <t xml:space="preserve">accepted.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2809,14 +2809,14 @@
       </c>
       <c r="F79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…もう少しだけ</t>
+          <t xml:space="preserve">…ありがとう。…世話になった</t>
         </is>
       </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">defended.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="F80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトを持てた。…十分だよ</t>
+          <t xml:space="preserve">…残るよ。…うん</t>
         </is>
       </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">defended.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2873,14 +2873,14 @@
       </c>
       <c r="F81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……潮時、だね</t>
+          <t xml:space="preserve">…ありがとう。…助かる</t>
         </is>
       </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.quiet.composed[1]</t>
+          <t xml:space="preserve">defense_failed.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2905,14 +2905,14 @@
       </c>
       <c r="F82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん</t>
+          <t xml:space="preserve">…ごめん…</t>
         </is>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet.composed[1]</t>
+          <t xml:space="preserve">defense_failed.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2937,14 +2937,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん</t>
+          <t xml:space="preserve">…じゃあね</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.quiet.composed[1]</t>
+          <t xml:space="preserve">default.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう、だね</t>
+          <t xml:space="preserve">…もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">former_champ.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3001,14 +3001,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このベルトがある限りは</t>
+          <t xml:space="preserve">…もう一度だけ</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.quiet.composed[1]</t>
+          <t xml:space="preserve">heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3033,14 +3033,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう、か</t>
+          <t xml:space="preserve">……いいよ</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.quiet.composed[1]</t>
+          <t xml:space="preserve">high_trust.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3065,14 +3065,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、闘える</t>
+          <t xml:space="preserve">…ありがとう。…もう少しだけ</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3097,14 +3097,14 @@
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ辞めない</t>
+          <t xml:space="preserve">…ベルトを持てた。…十分だよ</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3129,14 +3129,14 @@
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの重さ、忘れないよ</t>
+          <t xml:space="preserve">……潮時、だね</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3161,14 +3161,14 @@
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔いはない。…うん、ないよ</t>
+          <t xml:space="preserve">……うん</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3193,14 +3193,14 @@
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…じゃあね</t>
+          <t xml:space="preserve">……うん</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_winless.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3225,14 +3225,14 @@
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…うん</t>
+          <t xml:space="preserve">……そう、だね</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、なのにな</t>
+          <t xml:space="preserve">…このベルトがある限りは</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3289,14 +3289,14 @@
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…これからだったんだけどな</t>
+          <t xml:space="preserve">……そう、か</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3321,14 +3321,14 @@
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…十分だよ</t>
+          <t xml:space="preserve">…まだ、闘える</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、返したくなかった</t>
+          <t xml:space="preserve">…まだ辞めない</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">A1_champion.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここで。…うん</t>
+          <t xml:space="preserve">…あの重さ、忘れないよ</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3402,29 +3402,29 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう…ございます。…嬉しい。…頑張るね。</t>
+          <t xml:space="preserve">…悔いはない。…うん、ないよ</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3434,29 +3434,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">A3_heel.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……それだけでも…ありがたいです。…ちゃんと覚えてるよ。</t>
+          <t xml:space="preserve">…じゃあね</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3466,29 +3466,29 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう…。…分かった。…仕方ないね。</t>
+          <t xml:space="preserve">…ありがとう。…うん</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3498,29 +3498,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet.composed[1]</t>
+          <t xml:space="preserve">B1_young.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長、少しだけ。{tenure}…お給料のこと…落ち着いて話せるうちに、伝えておきたくて。</t>
+          <t xml:space="preserve">…まだ、なのにな</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3530,29 +3530,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">B2_prime.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう…。…分かりました。…少し、残念かな。</t>
+          <t xml:space="preserve">…これからだったんだけどな</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3562,29 +3562,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet.composed[1]</t>
+          <t xml:space="preserve">B3_older.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。{tenure}…離れたいの。…静かに決めたことだから。</t>
+          <t xml:space="preserve">…十分だよ</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3594,29 +3594,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんね…。…もう、決めたから。…静かに行かせて。</t>
+          <t xml:space="preserve">…まだ、返したくなかった</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3626,29 +3626,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまで…してくれるんだ。…もう少しだけ…頑張ってみるね。</t>
+          <t xml:space="preserve">……ここで。…うん</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_accept.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けない。ここにいる</t>
+          <t xml:space="preserve">……ありがとう…ございます。…嬉しい。…頑張るね。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる</t>
+          <t xml:space="preserve">……それだけでも…ありがたいです。…ちゃんと覚えてるよ。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞くよ</t>
+          <t xml:space="preserve">……そう…。…分かった。…仕方ないね。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_open.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。よろしく</t>
+          <t xml:space="preserve">……社長、少しだけ。{tenure}…お給料のこと…落ち着いて話せるうちに、伝えておきたくて。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3786,29 +3786,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……変わった、かな</t>
+          <t xml:space="preserve">……そう…。…分かりました。…少し、残念かな。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3818,29 +3818,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（……見えた。…次の一手——）</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が…見えなくなってね。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3850,29 +3850,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_open.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここまでだね</t>
+          <t xml:space="preserve">……社長。{tenure}…離れたいの。…静かに決めたことだから。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3882,29 +3882,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_release.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここまで来たんだね</t>
+          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}…世話になったね。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3914,29 +3914,29 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少しは、ね</t>
+          <t xml:space="preserve">……ごめんね…。…もう、決めたから。…静かに行かせて。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3946,29 +3946,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_success.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここか</t>
+          <t xml:space="preserve">……そこまで…してくれるんだ。…もう少しだけ…頑張ってみるね。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3978,29 +3978,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">blocked.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてる人が増えた、のかな</t>
+          <t xml:space="preserve">…動けない。ここにいる</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4010,29 +4010,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.quiet.composed[1]</t>
+          <t xml:space="preserve">fail.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ん。…ありがたいね</t>
+          <t xml:space="preserve">…ここにいる</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4042,29 +4042,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">start.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……闘う理由が、見えなくなった</t>
+          <t xml:space="preserve">……聞くよ</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4074,29 +4074,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">success.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう一度、やれそうだ</t>
+          <t xml:space="preserve">…行くよ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った、かな</t>
+          <t xml:space="preserve">……変わった、かな</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの負けから、少し…鈍い</t>
+          <t xml:space="preserve">（……見えた。…次の一手——）</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">fresh.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4185,14 +4185,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。…でも、まだ</t>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">heavy.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、少し遠い</t>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.quiet.composed[1]</t>
+          <t xml:space="preserve">warm.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4249,14 +4249,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。…心が、まだ</t>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4266,29 +4266,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">cap_reached.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
+          <t xml:space="preserve">……うん。…ここまでだね</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
+          <t xml:space="preserve">……うん。…ここまで来たんだね</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4330,29 +4330,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
+          <t xml:space="preserve">…少しは、ね</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4362,29 +4362,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.quiet.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">……うん。…ここか</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4394,29 +4394,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet.composed[1]</t>
+          <t xml:space="preserve">pop_growth.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ、やっただけ</t>
+          <t xml:space="preserve">…見てくれてる人が増えた、のかな</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4426,29 +4426,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.quiet.composed[1]</t>
+          <t xml:space="preserve">pop_star.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
+          <t xml:space="preserve">……ん。…ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
@@ -4468,19 +4468,19 @@
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドーム</t>
+          <t xml:space="preserve">……闘う理由が、見えなくなった</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4490,29 +4490,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備は、できています</t>
+          <t xml:space="preserve">……もう一度、やれそうだ</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4522,29 +4522,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立っている)</t>
+          <t xml:space="preserve">……戻った、かな</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4554,29 +4554,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">defeat.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">……あの負けから、少し…鈍い</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4586,29 +4586,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">injury_moderate_recovery.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よかった。本当によかった</t>
+          <t xml:space="preserve">……体は治った。…でも、まだ</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4618,29 +4618,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">injury_severe_recovery.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(しばし言葉を失う)</t>
+          <t xml:space="preserve">……リングが、少し遠い</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4650,29 +4650,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">penalty_end.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……体は治った。…心が、まだ</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">bestMatch.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4714,29 +4714,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">champion.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4746,29 +4746,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4778,29 +4778,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">mediaAward.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待っててくれ</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4810,29 +4810,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.quiet.composed[1]</t>
+          <t xml:space="preserve">mvp.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…一つずつ、やっただけ</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.composed[1]</t>
+          <t xml:space="preserve">rookie.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4874,29 +4874,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…ドーム</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4906,29 +4906,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[2]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">…準備は、できています</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[3]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4938,29 +4938,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[3]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待っててくれ</t>
+          <t xml:space="preserve">……(静かに立っている)</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4970,29 +4970,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5002,29 +5002,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[2]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">…よかった。本当によかった</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[3]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5034,29 +5034,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[3]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">……(しばし言葉を失う)</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5066,29 +5066,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.quiet.composed[1]</t>
+          <t xml:space="preserve">N1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5098,29 +5098,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">N2.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">…いい人たちだよ。…うん</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.quiet.composed[1]</t>
+          <t xml:space="preserve">N3.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">…少し、休むよ</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5162,29 +5162,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">N4.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">N5_low.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5226,29 +5226,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">N5_warning.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">…………なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5258,29 +5258,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">faction_decree.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">E1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">…出演の話か。…受けるよ</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">E6.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">S_boycott.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
+          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">S_boycott.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
+          <t xml:space="preserve">……悪いね…今日は……</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S_grumble.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">S_sns.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.composed[2]</t>
+          <t xml:space="preserve">S1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">S2.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.composed[2]</t>
+          <t xml:space="preserve">S3.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.composed[1]</t>
+          <t xml:space="preserve">S4_direct.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.composed[2]</t>
+          <t xml:space="preserve">S4_silent.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[1]</t>
+          <t xml:space="preserve">S5.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.composed[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[2]</t>
+          <t xml:space="preserve">S6.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.composed[1]</t>
+          <t xml:space="preserve">B1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.composed[2]</t>
+          <t xml:space="preserve">B2_fighter1.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.composed[2]</t>
+          <t xml:space="preserve">B4_brand.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+          <t xml:space="preserve">…わかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_cm.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。…ありがとう</t>
+          <t xml:space="preserve">…うん。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_fan.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_fashion.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,29 +5962,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_variety.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。…行くよ</t>
+          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">B4.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行くよ</t>
+          <t xml:space="preserve">…わかった。…やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,29 +6026,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.composed[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
@@ -6068,19 +6068,19 @@
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構える）</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
@@ -6100,19 +6100,19 @@
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
@@ -6132,19 +6132,19 @@
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
@@ -6164,19 +6164,19 @@
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう</t>
+          <t xml:space="preserve">…戻る。待っててくれ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,29 +6186,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.quiet.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,29 +6218,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.quiet.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…うん</t>
+          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,59 +6250,2235 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">draftInterest.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…それだけ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftJoin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……やるべきことをやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…戻る。待っててくれ</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……足りなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……守った。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……足りなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……守った。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう終わり。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…遠くなったね</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう考えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…どうしても考えてしまうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そのことばかり考えてる</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここにいたいね。ずっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…この場所は、守りたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…（荷物をまとめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう、何も感じないな</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……優勝。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪くなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後。…行くよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……行くよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……了解</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに構える）</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…うん</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.quiet.composed[1]</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr" s="2">
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr" s="12">
+      <c r="D254" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.quiet.composed[1]</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr" s="2">
+      <c r="E254" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr" s="3">
+      <c r="F254" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……ここまで来た。…ありがとう</t>
         </is>
       </c>
     </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H188"/>
+  <autoFilter ref="A1:H256"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -320,7 +320,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.composed[1]</t>
+          <t xml:space="preserve">atk.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -352,7 +352,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.composed[2]</t>
+          <t xml:space="preserve">atk.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -384,7 +384,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.composed[3]</t>
+          <t xml:space="preserve">atk.composed.quiet[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -416,7 +416,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.quiet.composed[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.composed.quiet[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.quiet.composed[4]</t>
+          <t xml:space="preserve">atk.composed.quiet[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -448,7 +448,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.composed[1]</t>
+          <t xml:space="preserve">bigmove.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -480,7 +480,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.composed[2]</t>
+          <t xml:space="preserve">bigmove.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -512,7 +512,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.quiet.composed[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.quiet.composed[3]</t>
+          <t xml:space="preserve">bigmove.composed.quiet[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -544,7 +544,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.composed[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.composed[1]</t>
+          <t xml:space="preserve">climax.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -576,7 +576,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.quiet.composed[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.quiet.composed[2]</t>
+          <t xml:space="preserve">climax.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -608,7 +608,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.composed.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.quiet.hit[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed.hit[1]</t>
+          <t xml:space="preserve">composed.quiet.hit[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -640,7 +640,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.composed.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.quiet.hit[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed.hit[2]</t>
+          <t xml:space="preserve">composed.quiet.hit[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -672,7 +672,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.composed.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.quiet.win[1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed.win[1]</t>
+          <t xml:space="preserve">composed.quiet.win[1]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -704,7 +704,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.quiet.composed.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.composed.quiet.win[2]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed.win[2]</t>
+          <t xml:space="preserve">composed.quiet.win[2]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -736,7 +736,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -768,7 +768,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -800,7 +800,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -832,7 +832,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -864,7 +864,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -896,7 +896,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -960,7 +960,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -992,7 +992,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1024,7 +1024,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1056,7 +1056,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1088,7 +1088,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1120,7 +1120,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1152,7 +1152,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1184,7 +1184,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1216,7 +1216,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1248,7 +1248,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ahead.quiet.composed[1]</t>
+          <t xml:space="preserve">ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1280,7 +1280,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_PREMATCH_LINES.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">behind.quiet.composed[1]</t>
+          <t xml:space="preserve">behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1312,7 +1312,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.composed[1]</t>
+          <t xml:space="preserve">loser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1344,7 +1344,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.quiet.composed[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.composed[1]</t>
+          <t xml:space="preserve">winner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1376,7 +1376,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.quiet.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.composed[1]</t>
+          <t xml:space="preserve">loser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1408,7 +1408,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.quiet.composed[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.composed[1]</t>
+          <t xml:space="preserve">winner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1440,7 +1440,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1472,7 +1472,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.composed[1]</t>
+          <t xml:space="preserve">defender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1504,7 +1504,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1536,7 +1536,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.composed[1]</t>
+          <t xml:space="preserve">defender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1568,7 +1568,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.quiet.composed[1]</t>
+          <t xml:space="preserve">attacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1600,7 +1600,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.quiet.composed[1]</t>
+          <t xml:space="preserve">defender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1632,7 +1632,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.quiet.composed[1]</t>
+          <t xml:space="preserve">fateAttacker.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.quiet.composed[1]</t>
+          <t xml:space="preserve">fateDefender.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1696,7 +1696,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1728,7 +1728,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1760,7 +1760,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.quiet.composed[1]</t>
+          <t xml:space="preserve">fateLoser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1792,7 +1792,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.quiet.composed[1]</t>
+          <t xml:space="preserve">fateWinner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1824,7 +1824,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.quiet.composed[1]</t>
+          <t xml:space="preserve">loser.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1856,7 +1856,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.quiet.composed[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.quiet.composed[1]</t>
+          <t xml:space="preserve">winner.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1888,7 +1888,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.quiet.composed[1]</t>
+          <t xml:space="preserve">loserLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1920,7 +1920,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.quiet.composed[1]</t>
+          <t xml:space="preserve">winnerLines.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1952,7 +1952,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.quiet.composed[1]</t>
+          <t xml:space="preserve">WEEKLY_STORY_TICKER.awakening.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">awakening.quiet.composed[1]</t>
+          <t xml:space="preserve">awakening.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2752,7 +2752,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet.composed[1]</t>
+          <t xml:space="preserve">accepted.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr" s="2">
@@ -2784,7 +2784,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.quiet.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.quiet.composed[2]</t>
+          <t xml:space="preserve">accepted.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr" s="2">
@@ -2816,7 +2816,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet.composed[1]</t>
+          <t xml:space="preserve">defended.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr" s="2">
@@ -2848,7 +2848,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.quiet.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.quiet.composed[2]</t>
+          <t xml:space="preserve">defended.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr" s="2">
@@ -2880,7 +2880,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.composed[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet.composed[1]</t>
+          <t xml:space="preserve">defense_failed.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr" s="2">
@@ -2912,7 +2912,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.quiet.composed[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.quiet.composed[2]</t>
+          <t xml:space="preserve">defense_failed.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2944,7 +2944,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.default.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.default.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">default.quiet.composed[1]</t>
+          <t xml:space="preserve">default.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -2976,7 +2976,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">former_champ.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3008,7 +3008,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.heel.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heel.quiet.composed[1]</t>
+          <t xml:space="preserve">heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3040,7 +3040,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.high_trust.quiet.composed[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.high_trust.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">high_trust.quiet.composed[1]</t>
+          <t xml:space="preserve">high_trust.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3072,7 +3072,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_former_champ.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_former_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_former_champ.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3104,7 +3104,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3136,7 +3136,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_no_title.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_no_title.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_no_title.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3168,7 +3168,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_terminal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3200,7 +3200,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_winless.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_winless.quiet.composed[1]</t>
+          <t xml:space="preserve">accept_winless.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3232,7 +3232,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_champ.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3264,7 +3264,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_distrust.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_distrust.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_distrust.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3296,7 +3296,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_fighting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_fighting.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_fighting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3328,7 +3328,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">refuse_heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3360,7 +3360,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.quiet.composed[1]</t>
+          <t xml:space="preserve">A1_champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3392,7 +3392,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.quiet.composed[1]</t>
+          <t xml:space="preserve">A2_uncrowned.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3424,7 +3424,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.quiet.composed[1]</t>
+          <t xml:space="preserve">A3_heel.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3456,7 +3456,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.quiet.composed[1]</t>
+          <t xml:space="preserve">A4_veteran.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3488,7 +3488,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.quiet.composed[1]</t>
+          <t xml:space="preserve">B1_young.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3520,7 +3520,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.quiet.composed[1]</t>
+          <t xml:space="preserve">B2_prime.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3552,7 +3552,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.quiet.composed[1]</t>
+          <t xml:space="preserve">B3_older.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3584,7 +3584,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.quiet.composed[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_champion_injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3616,7 +3616,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3648,7 +3648,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3680,7 +3680,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3712,7 +3712,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3744,7 +3744,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3776,7 +3776,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.quiet.composed[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3808,7 +3808,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.quiet.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が…見えなくなってね。</t>
+          <t xml:space="preserve">……すみません。…もう、限界でね。…さようなら。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.quiet.composed[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3865,14 +3865,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。{tenure}…離れたいの。…静かに決めたことだから。</t>
+          <t xml:space="preserve">…黙って出ていこうかと思ったけど。…一応、挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}…世話になったね。</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が…見えなくなってね。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんね…。…もう、決めたから。…静かに行かせて。</t>
+          <t xml:space="preserve">……社長。{tenure}…離れたいの。…静かに決めたことだから。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまで…してくれるんだ。…もう少しだけ…頑張ってみるね。</t>
+          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}…世話になったね。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けない。ここにいる</t>
+          <t xml:space="preserve">……ごめんね…。…もう、決めたから。…静かに行かせて。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.quiet.composed[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.quiet.composed[1]</t>
+          <t xml:space="preserve">transfer_retain_success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる</t>
+          <t xml:space="preserve">……そこまで…してくれるんだ。…もう少しだけ…頑張ってみるね。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.quiet.composed[1]</t>
+          <t xml:space="preserve">blocked.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞くよ</t>
+          <t xml:space="preserve">…動けない。ここにいる</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.quiet.composed[1]</t>
+          <t xml:space="preserve">fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。よろしく</t>
+          <t xml:space="preserve">…ここにいる</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,29 +4106,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">start.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……変わった、かな</t>
+          <t xml:space="preserve">……聞くよ</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,29 +4138,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（……見えた。…次の一手——）</t>
+          <t xml:space="preserve">…行くよ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,29 +4170,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.quiet.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
+          <t xml:space="preserve">…社長、私たちのこと、気に留めていただけると嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4202,29 +4202,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.quiet.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
+          <t xml:space="preserve">…社長、次のメイン、私たちで考えてみたいのですが。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4234,29 +4234,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.quiet.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
+          <t xml:space="preserve">…社長、給与改定のこと、ご相談したいのですが。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4266,29 +4266,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.quiet.composed[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここまでだね</t>
+          <t xml:space="preserve">…社長、私たちの働き、ご覧になっていますか。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここまで来たんだね</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくださったんですね、安心しました。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4330,29 +4330,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少しは、ね</t>
+          <t xml:space="preserve">…はい、すみません。出直します。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4362,29 +4362,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここか</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4394,29 +4394,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてる人が増えた、のかな</t>
+          <t xml:space="preserve">…ありがとうございます。やらせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4426,29 +4426,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ん。…ありがたいね</t>
+          <t xml:space="preserve">…はい、わかりました。出直します。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4458,29 +4458,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……闘う理由が、見えなくなった</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4490,29 +4490,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう一度、やれそうだ</t>
+          <t xml:space="preserve">…ありがとうございます。みんな、安心します。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4522,29 +4522,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った、かな</t>
+          <t xml:space="preserve">…はい、わかりました。出直します。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4554,29 +4554,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの負けから、少し…鈍い</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4586,29 +4586,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。…でも、まだ</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4618,29 +4618,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、少し遠い</t>
+          <t xml:space="preserve">…はい、わかりました。出直します。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4650,29 +4650,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。…心が、まだ</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4682,29 +4682,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
+          <t xml:space="preserve">…はい、…悪気はなかったんですが、配慮が足りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4714,29 +4714,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4746,29 +4746,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4778,29 +4778,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4810,29 +4810,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ、やっただけ</t>
+          <t xml:space="preserve">…はい、…やりすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
+          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4874,29 +4874,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドーム</t>
+          <t xml:space="preserve">…申し訳ありません。…出直します。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4906,29 +4906,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備は、できています</t>
+          <t xml:space="preserve">…ありがとうございます。…お気遣い、痛み入ります。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4938,29 +4938,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立っている)</t>
+          <t xml:space="preserve">…ありがとうございます。…私の代わりに、みんなを見てくださって。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4970,29 +4970,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…ありがとうございます。…お気遣い、頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5002,29 +5002,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よかった。本当によかった</t>
+          <t xml:space="preserve">…はい、…まだ、平気です。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.quiet.composed[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5034,29 +5034,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[3]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(しばし言葉を失う)</t>
+          <t xml:space="preserve">…ありがとうございます。…メンバーに支えてもらえると、楽になります。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5066,29 +5066,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5098,29 +5098,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい人たちだよ。…うん</t>
+          <t xml:space="preserve">…ありがとうございます。…ほっとしました。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5130,29 +5130,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休むよ</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子のケア、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5162,29 +5162,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5194,29 +5194,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
+          <t xml:space="preserve">（黙って、視線を落とした）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5226,29 +5226,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………なんでもないよ</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5258,29 +5258,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか</t>
+          <t xml:space="preserve">…はい、…緩めます。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5290,29 +5290,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話か。…受けるよ</t>
+          <t xml:space="preserve">…ありがとうございます。…見守ってください。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.quiet.composed[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5322,29 +5322,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.quiet.composed[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子、限界が近かったかもしれません。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.composed[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.composed</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,29 +5354,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.quiet.composed[1]</t>
+          <t xml:space="preserve">quiet.attack.composed</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
+          <t xml:space="preserve">……もう、戻れない</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.quiet.composed[2]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.composed</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.quiet.composed[2]</t>
+          <t xml:space="preserve">quiet.defend.composed</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いね…今日は……</t>
+          <t xml:space="preserve">そちらが望むなら</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.quiet.composed[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
+          <t xml:space="preserve">……変わった、かな</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.quiet.composed[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">（……見えた。…次の一手——）</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.quiet.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.quiet.composed[1]</t>
+          <t xml:space="preserve">fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.quiet.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.quiet.composed[1]</t>
+          <t xml:space="preserve">heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.quiet.composed[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.quiet.composed[1]</t>
+          <t xml:space="preserve">warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.quiet.composed[1]</t>
+          <t xml:space="preserve">cap_reached.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
+          <t xml:space="preserve">……うん。…ここまでだね</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.quiet.composed[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
+          <t xml:space="preserve">……うん。…ここまで来たんだね</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5642,29 +5642,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.quiet.composed[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
+          <t xml:space="preserve">…少しは、ね</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5674,29 +5674,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.quiet.composed[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
+          <t xml:space="preserve">……うん。…ここか</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5706,29 +5706,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.quiet.composed[1]</t>
+          <t xml:space="preserve">pop_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
+          <t xml:space="preserve">…見てくれてる人が増えた、のかな</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.quiet.composed[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,29 +5738,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.quiet.composed[1]</t>
+          <t xml:space="preserve">pop_star.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
+          <t xml:space="preserve">……ん。…ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.quiet.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,29 +5770,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
+          <t xml:space="preserve">……闘う理由が、見えなくなった</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.quiet.composed[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5802,29 +5802,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…やるよ</t>
+          <t xml:space="preserve">……もう一度、やれそうだ</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,29 +5834,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。…やるよ</t>
+          <t xml:space="preserve">……戻った、かな</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,29 +5866,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.quiet.composed[1]</t>
+          <t xml:space="preserve">defeat.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
+          <t xml:space="preserve">……あの負けから、少し…鈍い</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.quiet.composed[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
+          <t xml:space="preserve">……体は治った。…でも、まだ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,29 +5930,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.quiet.composed[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
+          <t xml:space="preserve">……リングが、少し遠い</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.quiet.composed[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,29 +5962,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.quiet.composed[1]</t>
+          <t xml:space="preserve">penalty_end.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
+          <t xml:space="preserve">……体は治った。…心が、まだ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.quiet.composed[1]</t>
+          <t xml:space="preserve">bestMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…やってみるよ</t>
+          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,29 +6026,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,29 +6090,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">mediaAward.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,29 +6122,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">mvp.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">…一つずつ、やっただけ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">rookie.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待っててくれ</t>
+          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,29 +6186,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
+          <t xml:space="preserve">…ドーム</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,29 +6218,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
+          <t xml:space="preserve">…準備は、できています</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,29 +6250,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……(静かに立っている)</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,29 +6282,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,29 +6314,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">…よかった。本当によかった</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet.composed[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6346,29 +6346,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……(しばし言葉を失う)</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6378,29 +6378,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.quiet.composed[1]</t>
+          <t xml:space="preserve">N1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6410,29 +6410,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.quiet.composed[1]</t>
+          <t xml:space="preserve">N2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
+          <t xml:space="preserve">…いい人たちだよ。…うん</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6442,29 +6442,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.quiet.composed[1]</t>
+          <t xml:space="preserve">N3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
+          <t xml:space="preserve">…少し、休むよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6474,29 +6474,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.quiet.composed[1]</t>
+          <t xml:space="preserve">N4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
+          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6506,29 +6506,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet.composed[1]</t>
+          <t xml:space="preserve">N5_low.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待っててくれ</t>
+          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet.composed[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6538,29 +6538,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet.composed[1]</t>
+          <t xml:space="preserve">N5_warning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">…………なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6570,29 +6570,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">faction_decree.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6602,29 +6602,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.quiet.composed[1]</t>
+          <t xml:space="preserve">E1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
+          <t xml:space="preserve">…出演の話か。…受けるよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6634,29 +6634,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">E6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6666,29 +6666,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.quiet.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6698,29 +6698,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.quiet.composed[1]</t>
+          <t xml:space="preserve">S_boycott.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">……悪いね…今日は……</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6730,29 +6730,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.quiet.composed[1]</t>
+          <t xml:space="preserve">S_grumble.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6762,29 +6762,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S_sns.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6794,29 +6794,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6826,29 +6826,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6858,29 +6858,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6890,29 +6890,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S4_direct.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6922,29 +6922,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">S4_silent.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6954,29 +6954,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
+          <t xml:space="preserve">S5.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わり。…それだけ</t>
+          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6986,29 +6986,29 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
+          <t xml:space="preserve">S6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…遠くなったね</t>
+          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7018,29 +7018,29 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
+          <t xml:space="preserve">B1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
+          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7050,29 +7050,29 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
+          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7082,29 +7082,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
+          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7114,29 +7114,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_brand.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう考えない</t>
+          <t xml:space="preserve">…わかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7146,29 +7146,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
+          <t xml:space="preserve">B4_cm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
+          <t xml:space="preserve">…うん。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7178,29 +7178,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_fan.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どうしても考えてしまうね</t>
+          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7210,29 +7210,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
+          <t xml:space="preserve">B4_fashion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
+          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7242,29 +7242,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
+          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7274,29 +7274,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
+          <t xml:space="preserve">B4_variety.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そのことばかり考えてる</t>
+          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7306,29 +7306,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
+          <t xml:space="preserve">B4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
+          <t xml:space="preserve">…わかった。…やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7338,29 +7338,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいたいね。ずっと</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,29 +7402,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この場所は、守りたい</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7434,29 +7434,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（荷物をまとめている）</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7466,29 +7466,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、何も感じないな</t>
+          <t xml:space="preserve">…戻る。待っててくれ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7498,29 +7498,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
+          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7530,29 +7530,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">draftInterest.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.composed[2]</t>
+          <t xml:space="preserve">draftJoin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7626,29 +7626,29 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">faGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7658,29 +7658,29 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.composed[2]</t>
+          <t xml:space="preserve">faSigning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7690,29 +7690,29 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.composed[1]</t>
+          <t xml:space="preserve">faWelcome.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7722,29 +7722,29 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.quiet.composed[2]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7754,29 +7754,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7786,29 +7786,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[2]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7818,29 +7818,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.composed[1]</t>
+          <t xml:space="preserve">injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+          <t xml:space="preserve">…戻る。待っててくれ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7850,29 +7850,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.quiet.composed[2]</t>
+          <t xml:space="preserve">release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7882,29 +7882,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.composed[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7914,29 +7914,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.quiet.composed[2]</t>
+          <t xml:space="preserve">scoutGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7946,29 +7946,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.quiet.composed[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。…ありがとう</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7978,29 +7978,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.quiet.composed[1]</t>
+          <t xml:space="preserve">titleDefense.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……守った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8010,29 +8010,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.quiet.composed[1]</t>
+          <t xml:space="preserve">titleLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8042,29 +8042,29 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.quiet.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8074,29 +8074,29 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。…行くよ</t>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8106,29 +8106,29 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行くよ</t>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8138,29 +8138,29 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8170,29 +8170,29 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構える）</t>
+          <t xml:space="preserve">……守った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8202,29 +8202,29 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8234,29 +8234,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8266,29 +8266,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう</t>
+          <t xml:space="preserve">…もう終わり。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,29 +8298,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">…遠くなったね</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8330,29 +8330,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…うん</t>
+          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…それだけ</t>
+          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,29 +8426,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">…もう考えない</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8458,27 +8458,1339 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…どうしても考えてしまうね</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そのことばかり考えてる</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="40" customHeight="1">
+      <c r="A261" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="40" customHeight="1">
+      <c r="A262" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="40" customHeight="1">
+      <c r="A263" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここにいたいね。ずっと</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="40" customHeight="1">
+      <c r="A264" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…この場所は、守りたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="40" customHeight="1">
+      <c r="A265" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…（荷物をまとめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="40" customHeight="1">
+      <c r="A266" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう、何も感じないな</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="40" customHeight="1">
+      <c r="A267" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="40" customHeight="1">
+      <c r="A268" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="40" customHeight="1">
+      <c r="A269" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="40" customHeight="1">
+      <c r="A270" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="40" customHeight="1">
+      <c r="A271" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="40" customHeight="1">
+      <c r="A272" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="40" customHeight="1">
+      <c r="A273" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="40" customHeight="1">
+      <c r="A274" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="40" customHeight="1">
+      <c r="A275" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="40" customHeight="1">
+      <c r="A276" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="40" customHeight="1">
+      <c r="A277" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="40" customHeight="1">
+      <c r="A278" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="40" customHeight="1">
+      <c r="A279" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="40" customHeight="1">
+      <c r="A280" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="40" customHeight="1">
+      <c r="A281" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……優勝。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="40" customHeight="1">
+      <c r="A282" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postLose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="40" customHeight="1">
+      <c r="A283" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="40" customHeight="1">
+      <c r="A284" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">postWin.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……悪くなかった</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="40" customHeight="1">
+      <c r="A285" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……最後。…行くよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="40" customHeight="1">
+      <c r="A286" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……行くよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="40" customHeight="1">
+      <c r="A287" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">summon.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……了解</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="40" customHeight="1">
+      <c r="A288" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（静かに構える）</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="40" customHeight="1">
+      <c r="A289" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="40" customHeight="1">
+      <c r="A290" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="40" customHeight="1">
+      <c r="A291" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="40" customHeight="1">
+      <c r="A292" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="40" customHeight="1">
+      <c r="A293" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…うん</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="40" customHeight="1">
+      <c r="A294" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="40" customHeight="1">
+      <c r="A295" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="40" customHeight="1">
+      <c r="A296" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="40" customHeight="1">
+      <c r="A297" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">quiet.composed[1]</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr" s="2">
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr" s="3">
+      <c r="F297" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H256"/>
+  <autoFilter ref="A1:H297"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5984,7 +5984,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
@@ -6009,14 +6009,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
+          <t xml:space="preserve">みんながいたから勝てた。</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
@@ -6041,14 +6041,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
+          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6073,14 +6073,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
+          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.composed.quiet[1]</t>
+          <t xml:space="preserve">hallOfFame.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6105,14 +6105,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.quiet[1]</t>
+          <t xml:space="preserve">mediaAward.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6137,14 +6137,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ、やっただけ</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.quiet[1]</t>
+          <t xml:space="preserve">mvp.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6169,14 +6169,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
+          <t xml:space="preserve">…一つずつ、やっただけ</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">rookie.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドーム</t>
+          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6218,12 +6218,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[2]</t>
+          <t xml:space="preserve">springTagChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備は、できています</t>
+          <t xml:space="preserve">相棒がいたからだ。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[3]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6265,14 +6265,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(静かに立っている)</t>
+          <t xml:space="preserve">…ドーム</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…準備は、できています</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[2]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よかった。本当によかった</t>
+          <t xml:space="preserve">……（静かに立っている）</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[3]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6361,14 +6361,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……(しばし言葉を失う)</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6378,29 +6378,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
+          <t xml:space="preserve">…よかった。本当によかった</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6410,29 +6410,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい人たちだよ。…うん</t>
+          <t xml:space="preserve">……（しばし言葉を失う）</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.quiet[1]</t>
+          <t xml:space="preserve">N1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6457,14 +6457,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休むよ</t>
+          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.quiet[1]</t>
+          <t xml:space="preserve">N2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6489,14 +6489,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
+          <t xml:space="preserve">…いい人たちだよ。…うん</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.quiet[1]</t>
+          <t xml:space="preserve">N3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6521,14 +6521,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
+          <t xml:space="preserve">…少し、休むよ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.quiet[1]</t>
+          <t xml:space="preserve">N4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6553,14 +6553,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………なんでもないよ</t>
+          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6570,29 +6570,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.quiet[1]</t>
+          <t xml:space="preserve">N5_low.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか</t>
+          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6602,29 +6602,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.quiet[1]</t>
+          <t xml:space="preserve">N5_warning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話か。…受けるよ</t>
+          <t xml:space="preserve">…………なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.quiet[1]</t>
+          <t xml:space="preserve">faction_decree.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6649,14 +6649,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.quiet[1]</t>
+          <t xml:space="preserve">E1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6681,14 +6681,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
+          <t xml:space="preserve">…出演の話か。…受けるよ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.quiet[2]</t>
+          <t xml:space="preserve">E6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6713,14 +6713,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いね…今日は……</t>
+          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
+          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6777,14 +6777,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">……悪いね…今日は……</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.quiet[1]</t>
+          <t xml:space="preserve">S_grumble.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6809,14 +6809,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
+          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.quiet[1]</t>
+          <t xml:space="preserve">S_sns.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6841,14 +6841,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
+          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.quiet[1]</t>
+          <t xml:space="preserve">S1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6873,14 +6873,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
+          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.quiet[1]</t>
+          <t xml:space="preserve">S2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6905,14 +6905,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
+          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.quiet[1]</t>
+          <t xml:space="preserve">S3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6937,14 +6937,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
+          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.quiet[1]</t>
+          <t xml:space="preserve">S4_direct.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
+          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.quiet[1]</t>
+          <t xml:space="preserve">S4_silent.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7001,14 +7001,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
+          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.quiet[1]</t>
+          <t xml:space="preserve">S5.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
+          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.quiet[1]</t>
+          <t xml:space="preserve">S6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
+          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.quiet[1]</t>
+          <t xml:space="preserve">B1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
+          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…やるよ</t>
+          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。…やるよ</t>
+          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.quiet[1]</t>
+          <t xml:space="preserve">B4_brand.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
+          <t xml:space="preserve">…わかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.quiet[1]</t>
+          <t xml:space="preserve">B4_cm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
+          <t xml:space="preserve">…うん。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.quiet[1]</t>
+          <t xml:space="preserve">B4_fan.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7257,14 +7257,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
+          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.quiet[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
+          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.quiet[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…やってみるよ</t>
+          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7338,29 +7338,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4_variety.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7370,29 +7370,29 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…わかった。…やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
@@ -7424,7 +7424,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
@@ -7449,14 +7449,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
@@ -7481,14 +7481,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待っててくれ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7513,14 +7513,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7545,14 +7545,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
+          <t xml:space="preserve">…戻る。待ってて</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7577,14 +7577,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7609,14 +7609,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">draftInterest.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7641,14 +7641,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7673,14 +7673,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.quiet[1]</t>
+          <t xml:space="preserve">faSigning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7801,14 +7801,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待っててくれ</t>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">…戻る。待ってて</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8057,14 +8057,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……守った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">titleWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
@@ -8153,14 +8153,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
@@ -8185,14 +8185,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……守った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8266,29 +8266,29 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わり。…それだけ</t>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,29 +8298,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…遠くなったね</t>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
+          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
@@ -8345,14 +8345,14 @@
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
+          <t xml:space="preserve">…もう終わり。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
@@ -8377,14 +8377,14 @@
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
+          <t xml:space="preserve">…遠くなったね</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
@@ -8409,14 +8409,14 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
+          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう考えない</t>
+          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
+          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
+          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
@@ -8505,14 +8505,14 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どうしても考えてしまうね</t>
+          <t xml:space="preserve">…もう考えない</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
@@ -8537,14 +8537,14 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
+          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
+          <t xml:space="preserve">…どうしても考えてしまうね</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そのことばかり考えてる</t>
+          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
+          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
+          <t xml:space="preserve">…そのことばかり考えてる</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいたいね。ずっと</t>
+          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この場所は、守りたい</t>
+          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（荷物をまとめている）</t>
+          <t xml:space="preserve">…ここにいたいね。ずっと</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、何も感じないな</t>
+          <t xml:space="preserve">…この場所は、守りたい</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
+          <t xml:space="preserve">…（荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+          <t xml:space="preserve">…もう、何も感じないな</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8874,29 +8874,29 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8906,29 +8906,29 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.quiet[1]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9017,14 +9017,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.quiet[2]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9049,14 +9049,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">survivor.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9081,14 +9081,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[2]</t>
+          <t xml:space="preserve">survivor.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.quiet[2]</t>
+          <t xml:space="preserve">champion.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
+          <t xml:space="preserve">defiant.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9209,14 +9209,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
+          <t xml:space="preserve">defiant.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9273,14 +9273,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。…ありがとう</t>
+          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9305,14 +9305,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……優勝。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.quiet[1]</t>
+          <t xml:space="preserve">postLose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9369,14 +9369,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9401,14 +9401,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。…行くよ</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">postWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9433,14 +9433,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行くよ</t>
+          <t xml:space="preserve">……悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.quiet[1]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9465,14 +9465,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解</t>
+          <t xml:space="preserve">……最後。…行くよ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構える）</t>
+          <t xml:space="preserve">……行くよ</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">summon.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9529,14 +9529,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……了解</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
@@ -9561,14 +9561,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+          <t xml:space="preserve">……（静かに構える）</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
@@ -9593,14 +9593,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう</t>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……対抗戦を。…よろしく</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9657,14 +9657,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…うん</t>
+          <t xml:space="preserve">……そう</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9689,14 +9689,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…それだけ</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9706,29 +9706,29 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+          <t xml:space="preserve">result_win.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+          <t xml:space="preserve">……勝った。…うん</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
@@ -9748,49 +9748,113 @@
       </c>
       <c r="E296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">……勝った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="40" customHeight="1">
+      <c r="A298" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="40" customHeight="1">
+      <c r="A299" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.quiet[1]</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr" s="2">
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr" s="12">
+      <c r="D299" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr" s="2">
+      <c r="E299" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr" s="3">
+      <c r="F299" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H297"/>
+  <autoFilter ref="A1:H299"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3648,7 +3648,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.composed.quiet[1]</t>
+          <t xml:space="preserve">decline_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう…ございます。…嬉しい。…頑張るね。</t>
+          <t xml:space="preserve">……うん。……はんこ、押すね。……それだけのことだから。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.composed.quiet[1]</t>
+          <t xml:space="preserve">decline_hold.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3705,14 +3705,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……それだけでも…ありがたいです。…ちゃんと覚えてるよ。</t>
+          <t xml:space="preserve">……据え置き……？ ……社長、損するよ？ ……ううん。……ありがとう。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.composed.quiet[1]</t>
+          <t xml:space="preserve">decline_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3737,14 +3737,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう…。…分かった。…仕方ないね。</t>
+          <t xml:space="preserve">……そう。……数字、見せてもらえる？ ……口で言われるより、早いから。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.composed.quiet[1]</t>
+          <t xml:space="preserve">decline_strict.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長、少しだけ。{tenure}…お給料のこと…落ち着いて話せるうちに、伝えておきたくて。</t>
+          <t xml:space="preserve">…………そう。……分かった。……話は、それだけ？</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.composed.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう…。…分かりました。…少し、残念かな。</t>
+          <t xml:space="preserve">……ん。……気を遣われなくて、よかった。……そのほうが、背筋が伸びる。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.quiet[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません。…もう、限界でね。…さようなら。</t>
+          <t xml:space="preserve">……下げて、って言ったのに。……ずるいよ？ ……うん。……返す。ちゃんと、返す。</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.quiet[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.composed.quiet[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3865,14 +3865,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…黙って出ていこうかと思ったけど。…一応、挨拶だけ。辞めます。</t>
+          <t xml:space="preserve">……社長。……査定、下げていいよ。……自分の体だから。……一番、分かってる。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.composed.quiet[1]</t>
+          <t xml:space="preserve">raise_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が…見えなくなってね。</t>
+          <t xml:space="preserve">……ありがとう…ございます。…嬉しい。…頑張るね。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.composed.quiet[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3929,14 +3929,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……社長。{tenure}…離れたいの。…静かに決めたことだから。</t>
+          <t xml:space="preserve">……それだけでも…ありがたいです。…ちゃんと覚えてるよ。</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.composed.quiet[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}…世話になったね。</t>
+          <t xml:space="preserve">……そう…。…分かった。…仕方ないね。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.composed.quiet[1]</t>
+          <t xml:space="preserve">raise_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめんね…。…もう、決めたから。…静かに行かせて。</t>
+          <t xml:space="preserve">……社長、少しだけ。{tenure}…お給料のこと…落ち着いて話せるうちに、伝えておきたくて。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.composed.quiet[1]</t>
+          <t xml:space="preserve">raise_refuse.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
@@ -4025,14 +4025,14 @@
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そこまで…してくれるんだ。…もう少しだけ…頑張ってみるね。</t>
+          <t xml:space="preserve">……そう…。…分かりました。…少し、残念かな。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">blocked.composed.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…動けない。ここにいる</t>
+          <t xml:space="preserve">……すみません。…もう、限界でね。…さようなら。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fail.composed.quiet[1]</t>
+          <t xml:space="preserve">sudden_departure.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいる</t>
+          <t xml:space="preserve">…黙って出ていこうかと思ったけど。…一応、挨拶だけ。辞めます。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.composed.quiet[1]</t>
+          <t xml:space="preserve">transfer_listen.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……聞くよ</t>
+          <t xml:space="preserve">…聞いてくれるんだ。{record}…ここにいる意味が…見えなくなってね。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">success.composed.quiet[1]</t>
+          <t xml:space="preserve">transfer_open.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…行くよ。よろしく</t>
+          <t xml:space="preserve">……社長。{tenure}…離れたいの。…静かに決めたことだから。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4170,29 +4170,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.quiet[1]</t>
+          <t xml:space="preserve">transfer_release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちのこと、気に留めていただけると嬉しいです。</t>
+          <t xml:space="preserve">……ありがとう。{tenure_farewell}{rivalry}…世話になったね。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4202,29 +4202,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、次のメイン、私たちで考えてみたいのですが。</t>
+          <t xml:space="preserve">……ごめんね…。…もう、決めたから。…静かに行かせて。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.quiet[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4234,29 +4234,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.quiet[1]</t>
+          <t xml:space="preserve">transfer_retain_success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、給与改定のこと、ご相談したいのですが。</t>
+          <t xml:space="preserve">……そこまで…してくれるんだ。…もう少しだけ…頑張ってみるね。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.blocked.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4266,29 +4266,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.quiet[1]</t>
+          <t xml:space="preserve">blocked.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…社長、私たちの働き、ご覧になっていますか。</t>
+          <t xml:space="preserve">…動けない。ここにいる</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4298,29 +4298,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.quiet[1]</t>
+          <t xml:space="preserve">fail.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見ていてくださったんですね、安心しました。</t>
+          <t xml:space="preserve">…ここにいる</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4330,29 +4330,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.quiet[1]</t>
+          <t xml:space="preserve">start.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、すみません。出直します。</t>
+          <t xml:space="preserve">……聞くよ</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.quiet[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4362,29 +4362,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.quiet[1]</t>
+          <t xml:space="preserve">success.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
+          <t xml:space="preserve">…行くよ。よろしく</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4409,14 +4409,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。やらせていただきます。</t>
+          <t xml:space="preserve">…社長、私たちのこと、気に留めていただけると嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。出直します。</t>
+          <t xml:space="preserve">…社長、次のメイン、私たちで考えてみたいのですが。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4473,14 +4473,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
+          <t xml:space="preserve">…社長、給与改定のこと、ご相談したいのですが。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.quiet[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4505,14 +4505,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。みんな、安心します。</t>
+          <t xml:space="preserve">…社長、私たちの働き、ご覧になっていますか。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。出直します。</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくださったんですね、安心しました。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4569,14 +4569,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
+          <t xml:space="preserve">…はい、すみません。出直します。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4601,14 +4601,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見ていてくださったんですね。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4633,14 +4633,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、わかりました。出直します。</t>
+          <t xml:space="preserve">…ありがとうございます。やらせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
+          <t xml:space="preserve">…はい、わかりました。出直します。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…悪気はなかったんですが、配慮が足りませんでした。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4729,14 +4729,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
+          <t xml:space="preserve">…ありがとうございます。みんな、安心します。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…気をつけます。</t>
+          <t xml:space="preserve">…はい、わかりました。出直します。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…やりすぎでした。</t>
+          <t xml:space="preserve">…ありがとうございます。…見ていてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
+          <t xml:space="preserve">…はい、わかりました。出直します。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…申し訳ありません。…出直します。</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで考えてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…お気遣い、痛み入ります。</t>
+          <t xml:space="preserve">…はい、…悪気はなかったんですが、配慮が足りませんでした。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…私の代わりに、みんなを見てくださって。</t>
+          <t xml:space="preserve">…ありがとうございます。…でも、少し、考えます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…お気遣い、頂戴します。</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…まだ、平気です。</t>
+          <t xml:space="preserve">…ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…メンバーに支えてもらえると、楽になります。</t>
+          <t xml:space="preserve">…はい、…やりすぎでした。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…気をつけます。</t>
+          <t xml:space="preserve">…ありがとうございます。…ヒールの仕事、続けます。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…ほっとしました。</t>
+          <t xml:space="preserve">…申し訳ありません。…出直します。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…下の子のケア、ありがたいです。</t>
+          <t xml:space="preserve">…ありがとうございます。…お気遣い、痛み入ります。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…気をつけます。</t>
+          <t xml:space="preserve">…ありがとうございます。…私の代わりに、みんなを見てくださって。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（黙って、視線を落とした）</t>
+          <t xml:space="preserve">…ありがとうございます。…お気遣い、頂戴します。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくださったんですね。</t>
+          <t xml:space="preserve">…はい、…まだ、平気です。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…はい、…緩めます。</t>
+          <t xml:space="preserve">…ありがとうございます。…メンバーに支えてもらえると、楽になります。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…見守ってください。</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。…下の子、限界が近かったかもしれません。</t>
+          <t xml:space="preserve">…ありがとうございます。…ほっとしました。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.attack.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう、戻れない</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子のケア、ありがたいです。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.composed</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet.defend.composed</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そちらが望むなら</t>
+          <t xml:space="preserve">…はい、…気をつけます。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5418,29 +5418,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……変わった、かな</t>
+          <t xml:space="preserve">（黙って、視線を落とした）</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5450,29 +5450,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BT_HINT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（……見えた。…次の一手——）</t>
+          <t xml:space="preserve">…ありがとうございます。…そっちで動いてくださったんですね。</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5482,29 +5482,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fresh.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
+          <t xml:space="preserve">…はい、…緩めます。</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5514,29 +5514,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heavy.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
+          <t xml:space="preserve">…ありがとうございます。…見守ってください。</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.quiet[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5546,29 +5546,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warm.composed.quiet[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
+          <t xml:space="preserve">…ありがとうございます。…下の子、限界が近かったかもしれません。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.attack.composed</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5578,29 +5578,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">cap_reached.composed.quiet[1]</t>
+          <t xml:space="preserve">quiet.attack.composed</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここまでだね</t>
+          <t xml:space="preserve">……もう、戻れない</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.quiet[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.quiet.defend.composed</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5610,29 +5610,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_elite.composed.quiet[1]</t>
+          <t xml:space="preserve">quiet.defend.composed</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここまで来たんだね</t>
+          <t xml:space="preserve">そちらが望むなら</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.quiet[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5642,12 +5642,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_growth.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5657,14 +5657,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少しは、ね</t>
+          <t xml:space="preserve">……変わった、かな</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.quiet[1]</t>
+          <t xml:space="preserve">BT_HINT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">BT_HINT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ovr_legend.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5689,14 +5689,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……うん。…ここか</t>
+          <t xml:space="preserve">（……見えた。…次の一手——）</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_growth.composed.quiet[1]</t>
+          <t xml:space="preserve">fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5721,14 +5721,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてる人が増えた、のかな</t>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MILESTONE_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">pop_star.composed.quiet[1]</t>
+          <t xml:space="preserve">heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5753,14 +5753,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ん。…ありがたいね</t>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">HEAT_STATE_SELF_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5785,14 +5785,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……闘う理由が、見えなくなった</t>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.cap_reached.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">cap_reached.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
@@ -5817,14 +5817,14 @@
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう一度、やれそうだ</t>
+          <t xml:space="preserve">……うん。…ここまでだね</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_elite.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">ovr_elite.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
@@ -5849,14 +5849,14 @@
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った、かな</t>
+          <t xml:space="preserve">……うん。…ここまで来たんだね</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.composed.quiet[1]</t>
+          <t xml:space="preserve">ovr_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
@@ -5881,14 +5881,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの負けから、少し…鈍い</t>
+          <t xml:space="preserve">…少しは、ね</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.ovr_legend.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_moderate_recovery.composed.quiet[1]</t>
+          <t xml:space="preserve">ovr_legend.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5913,14 +5913,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。…でも、まだ</t>
+          <t xml:space="preserve">……うん。…ここか</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury_severe_recovery.composed.quiet[1]</t>
+          <t xml:space="preserve">pop_growth.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5945,14 +5945,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……リングが、少し遠い</t>
+          <t xml:space="preserve">…見てくれてる人が増えた、のかな</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.quiet[1]</t>
+          <t xml:space="preserve">MILESTONE_LINES.pop_star.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">MILESTONE_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">penalty_end.composed.quiet[1]</t>
+          <t xml:space="preserve">pop_star.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
@@ -5977,14 +5977,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体は治った。…心が、まだ</t>
+          <t xml:space="preserve">……ん。…ありがたいね</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5994,29 +5994,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんながいたから勝てた。</t>
+          <t xml:space="preserve">……闘う理由が、見えなくなった</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6026,29 +6026,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
+          <t xml:space="preserve">……もう一度、やれそうだ</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6058,29 +6058,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
+          <t xml:space="preserve">……戻った、かな</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6090,29 +6090,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.composed.quiet[1]</t>
+          <t xml:space="preserve">defeat.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
+          <t xml:space="preserve">……あの負けから、少し…鈍い</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_moderate_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6122,29 +6122,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.composed.quiet[1]</t>
+          <t xml:space="preserve">injury_moderate_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう</t>
+          <t xml:space="preserve">……体は治った。…でも、まだ</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.composed.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.injury_severe_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6154,29 +6154,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.composed.quiet[1]</t>
+          <t xml:space="preserve">injury_severe_recovery.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…一つずつ、やっただけ</t>
+          <t xml:space="preserve">……リングが、少し遠い</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.composed.quiet[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.penalty_end.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6186,29 +6186,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.composed.quiet[1]</t>
+          <t xml:space="preserve">penalty_end.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
+          <t xml:space="preserve">……体は治った。…心が、まだ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.composed.quiet[1]</t>
+          <t xml:space="preserve">autumnWarChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6233,14 +6233,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒がいたからだ。</t>
+          <t xml:space="preserve">みんながいたから勝てた。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">bestMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6265,14 +6265,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ドーム</t>
+          <t xml:space="preserve">……あの試合のことは、忘れないだろうね</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[2]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備は、できています</t>
+          <t xml:space="preserve">……この重さ、嫌いじゃない</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[3]</t>
+          <t xml:space="preserve">hallOfFame.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに立っている）</t>
+          <t xml:space="preserve">……ありがとう。…いい場所だった</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">mediaAward.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6361,14 +6361,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…満員</t>
+          <t xml:space="preserve">…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[2]</t>
+          <t xml:space="preserve">mvp.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6393,14 +6393,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よかった。本当によかった</t>
+          <t xml:space="preserve">…一つずつ、やっただけ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[3]</t>
+          <t xml:space="preserve">rookie.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6425,14 +6425,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（しばし言葉を失う）</t>
+          <t xml:space="preserve">…ありがとう。…まだ先があるから</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.quiet[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6442,29 +6442,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.composed.quiet[1]</t>
+          <t xml:space="preserve">springTagChampion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
+          <t xml:space="preserve">相棒がいたからだ。</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6474,29 +6474,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いい人たちだよ。…うん</t>
+          <t xml:space="preserve">…ドーム</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6506,29 +6506,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…少し、休むよ</t>
+          <t xml:space="preserve">…準備は、できています</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6538,29 +6538,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
+          <t xml:space="preserve">……（静かに立っている）</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6570,29 +6570,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
+          <t xml:space="preserve">…満員</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6602,29 +6602,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[2]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………なんでもないよ</t>
+          <t xml:space="preserve">…よかった。本当によかった</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.quiet[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.composed.quiet[3]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6634,29 +6634,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[3]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そうか</t>
+          <t xml:space="preserve">……（しばし言葉を失う）</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6666,29 +6666,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.composed.quiet[1]</t>
+          <t xml:space="preserve">N1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出演の話か。…受けるよ</t>
+          <t xml:space="preserve">…少し、手応えがある。…この調子かな</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6698,29 +6698,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.composed.quiet[1]</t>
+          <t xml:space="preserve">N2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
+          <t xml:space="preserve">…いい人たちだよ。…うん</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6730,29 +6730,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.quiet[1]</t>
+          <t xml:space="preserve">N3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
+          <t xml:space="preserve">…少し、休むよ</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6762,29 +6762,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.composed.quiet[2]</t>
+          <t xml:space="preserve">N4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いね…今日は……</t>
+          <t xml:space="preserve">…応援、ありがとう。…届いてるよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6794,29 +6794,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.composed.quiet[1]</t>
+          <t xml:space="preserve">N5_low.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
+          <t xml:space="preserve">………（何も言わず、窓の外を見ている）</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.quiet[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6826,29 +6826,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.composed.quiet[1]</t>
+          <t xml:space="preserve">N5_warning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
+          <t xml:space="preserve">…………なんでもないよ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.quiet[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6858,12 +6858,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.composed.quiet[1]</t>
+          <t xml:space="preserve">faction_decree.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6873,14 +6873,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
+          <t xml:space="preserve">……そうか</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.composed.quiet[1]</t>
+          <t xml:space="preserve">E1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6905,14 +6905,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
+          <t xml:space="preserve">…出演の話か。…受けるよ</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.composed.quiet[1]</t>
+          <t xml:space="preserve">E6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6937,14 +6937,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
+          <t xml:space="preserve">………他所から、話が来てるんだ（声を落として）</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.composed.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -6969,14 +6969,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
+          <t xml:space="preserve">…………（何も言わずに、道場の戸口へ向かっている）</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.composed.quiet[1]</t>
+          <t xml:space="preserve">S_boycott.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7001,14 +7001,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
+          <t xml:space="preserve">……悪いね…今日は……</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.composed.quiet[1]</t>
+          <t xml:space="preserve">S_grumble.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr" s="2">
@@ -7033,14 +7033,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
+          <t xml:space="preserve">（何も言わないが、その静けさがかえってロッカーを重くしている）</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.composed.quiet[1]</t>
+          <t xml:space="preserve">S_sns.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7065,14 +7065,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
+          <t xml:space="preserve">（SNSに何も書かず、夜の窓の写真だけを投稿。ファンがざわついている）</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.composed.quiet[1]</t>
+          <t xml:space="preserve">S1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7097,14 +7097,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
+          <t xml:space="preserve">……挑戦、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.composed.quiet[1]</t>
+          <t xml:space="preserve">S2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7129,14 +7129,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
+          <t xml:space="preserve">……あの人と、やらせてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.composed.quiet[1]</t>
+          <t xml:space="preserve">S3.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7161,14 +7161,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
+          <t xml:space="preserve">……休みたい。少しでいいんだ</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.composed.quiet[1]</t>
+          <t xml:space="preserve">S4_direct.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7193,14 +7193,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…やるよ</t>
+          <t xml:space="preserve">……黙ってたけどね。…このままは、無理だよ</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.composed.quiet[1]</t>
+          <t xml:space="preserve">S4_silent.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うん。…やるよ</t>
+          <t xml:space="preserve">…………（ひとつ息をついて、それきり黙っている）</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.composed.quiet[1]</t>
+          <t xml:space="preserve">S5.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7257,14 +7257,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
+          <t xml:space="preserve">……特訓、させてほしい。それだけ</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.quiet[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.composed.quiet[1]</t>
+          <t xml:space="preserve">S6.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7289,14 +7289,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
+          <t xml:space="preserve">……後輩に、渡したいものがあるんだ</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.composed.quiet[1]</t>
+          <t xml:space="preserve">B1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7321,14 +7321,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
+          <t xml:space="preserve">……ごめん。…すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.composed.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter1.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7353,14 +7353,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
+          <t xml:space="preserve">……あの人とは…もう、いいかな</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.composed.quiet[1]</t>
+          <t xml:space="preserve">B2_fighter2.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7385,14 +7385,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかった。…やってみるよ</t>
+          <t xml:space="preserve">………（黙ったまま、静かに息を吐いている）</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7402,29 +7402,29 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4_brand.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…わかった。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7434,29 +7434,29 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4_cm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…よろしく。精一杯やる</t>
+          <t xml:space="preserve">…うん。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7466,29 +7466,29 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4_fan.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">…ファンの人と話すんだね。…ちゃんとやるよ</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7498,29 +7498,29 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4_fashion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">…歩けばいいんだね。…やるよ</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7530,29 +7530,29 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">B4_gravure.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待ってて</t>
+          <t xml:space="preserve">…撮るだけだよね。…わかった</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7562,29 +7562,29 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.composed.quiet[1]</t>
+          <t xml:space="preserve">B4_variety.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
+          <t xml:space="preserve">…喋るんだね。…少し、緊張するかな</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.quiet[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7594,29 +7594,29 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.composed.quiet[1]</t>
+          <t xml:space="preserve">B4.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
+          <t xml:space="preserve">…わかった。…やってみるよ</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7648,7 +7648,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7680,7 +7680,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7705,14 +7705,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7737,14 +7737,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……よろしく</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やるべきことをやる</t>
+          <t xml:space="preserve">…戻る。待ってて</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.composed.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7801,14 +7801,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
+          <t xml:space="preserve">……もう済んだ。…なのに、目が探してしまう</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.composed.quiet[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7833,14 +7833,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
+          <t xml:space="preserve">……もう昔の話だ。…そう言えたら、楽だったな</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.composed.quiet[1]</t>
+          <t xml:space="preserve">draftInterest.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7865,14 +7865,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.composed.quiet[1]</t>
+          <t xml:space="preserve">draftJoin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…戻る。待ってて</t>
+          <t xml:space="preserve">…よろしく。精一杯やる</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.composed.quiet[1]</t>
+          <t xml:space="preserve">faGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。世話になった</t>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">faSigning.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……短い間だけど、よろしく</t>
+          <t xml:space="preserve">……よろしく</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.composed.quiet[1]</t>
+          <t xml:space="preserve">faWelcome.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -7993,14 +7993,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
+          <t xml:space="preserve">……やるべきことをやる</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8025,14 +8025,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">……体が軽い。…こういう日は、大事にしたいね</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.composed.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8057,14 +8057,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">……体が重い。…今日はやっても、こぼれるだけだね</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.composed.quiet[1]</t>
+          <t xml:space="preserve">heatSelf.warm.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8089,14 +8089,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">……手応えが、少し遠いかな。…気のせいだといいけど</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.composed.quiet[1]</t>
+          <t xml:space="preserve">injury.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8121,14 +8121,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">…戻る。待ってて</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">release.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8160,7 +8160,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">rentalGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8192,7 +8192,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">scoutGreeting.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった</t>
+          <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8249,14 +8249,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……守った。…それだけ</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">titleDefense.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8281,14 +8281,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
+          <t xml:space="preserve">……守った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">titleLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8330,29 +8330,29 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
+          <t xml:space="preserve">titleWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう終わり。…それだけ</t>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8362,29 +8362,29 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…遠くなったね</t>
+          <t xml:space="preserve">…ありがとう。世話になった</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8394,29 +8394,29 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
+          <t xml:space="preserve">……短い間だけど、よろしく</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8426,29 +8426,29 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8458,29 +8458,29 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
+          <t xml:space="preserve">……守った。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8490,29 +8490,29 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう考えない</t>
+          <t xml:space="preserve">……（静かにベルトを見送っている）</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8522,29 +8522,29 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
+          <t xml:space="preserve">……（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_39_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr" s="2">
@@ -8569,14 +8569,14 @@
       </c>
       <c r="F259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…どうしても考えてしまうね</t>
+          <t xml:space="preserve">…もう終わり。…それだけ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
+          <t xml:space="preserve">bond_59_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr" s="2">
@@ -8601,14 +8601,14 @@
       </c>
       <c r="F260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
+          <t xml:space="preserve">…遠くなったね</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_59_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8633,14 +8633,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
+          <t xml:space="preserve">…気づけば、隣にいない。…そういうものか</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
+          <t xml:space="preserve">bond_60_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8665,14 +8665,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そのことばかり考えてる</t>
+          <t xml:space="preserve">……居心地がいい。…静かでいい</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
+          <t xml:space="preserve">bond_80_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8697,14 +8697,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
+          <t xml:space="preserve">……そばにいてくれるだけで、十分だ</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8729,14 +8729,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
+          <t xml:space="preserve">…もう考えない</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_29_down.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいたいね。ずっと</t>
+          <t xml:space="preserve">…風が止んだ。…そんな感じだね</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8793,14 +8793,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この場所は、守りたい</t>
+          <t xml:space="preserve">…どうしても考えてしまうね</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_30_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8825,14 +8825,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…（荷物をまとめている）</t>
+          <t xml:space="preserve">…燃えてる。…自分の中の何かが</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8857,14 +8857,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう、何も感じないな</t>
+          <t xml:space="preserve">…認めたくないけど、意識してるね</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
+          <t xml:space="preserve">rivalry_50_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -8889,14 +8889,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
+          <t xml:space="preserve">…そのことばかり考えてる</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+          <t xml:space="preserve">…あの人がいる限り、リングに立ち続けるよ</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8938,29 +8938,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">rivalry_70_up.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+          <t xml:space="preserve">…言葉はいらない。…リングで話そうか</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8970,29 +8970,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
+          <t xml:space="preserve">trust_above_75.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+          <t xml:space="preserve">…ここにいたいね。ずっと</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9002,29 +9002,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">trust_above_75.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+          <t xml:space="preserve">…この場所は、守りたい</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9034,29 +9034,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
+          <t xml:space="preserve">trust_below_20.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+          <t xml:space="preserve">…（荷物をまとめている）</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.quiet.composed[2]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9066,29 +9066,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.quiet[1]</t>
+          <t xml:space="preserve">trust_below_20.quiet.composed[2]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">…もう、何も感じないな</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.quiet.composed[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9098,29 +9098,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.quiet[2]</t>
+          <t xml:space="preserve">trust_below_35.quiet.composed[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+          <t xml:space="preserve">…ここにいていいのか。…分からなくなってきたね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9130,29 +9130,29 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[2]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.quiet[1]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9209,14 +9209,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.quiet[2]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9273,14 +9273,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
+          <t xml:space="preserve">survivor.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9305,14 +9305,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9322,12 +9322,12 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">survivor.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。…ありがとう</t>
+          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9354,12 +9354,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9369,14 +9369,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9401,14 +9401,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.quiet[1]</t>
+          <t xml:space="preserve">defiant.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9433,14 +9433,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">defiant.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9465,14 +9465,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。…行くよ</t>
+          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行くよ</t>
+          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9529,14 +9529,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解</t>
+          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9561,14 +9561,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構える）</t>
+          <t xml:space="preserve">……優勝。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">postLose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9593,14 +9593,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">postWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9657,14 +9657,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう</t>
+          <t xml:space="preserve">……悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9689,14 +9689,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……最後。…行くよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.quiet[1]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9721,14 +9721,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…うん</t>
+          <t xml:space="preserve">……行くよ</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">summon.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9753,14 +9753,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…それだけ</t>
+          <t xml:space="preserve">……了解</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9770,29 +9770,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+          <t xml:space="preserve">……（静かに構える）</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9812,49 +9812,273 @@
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…うん</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="40" customHeight="1">
+      <c r="A306" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.quiet[1]</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr" s="2">
+      <c r="B306" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr" s="12">
+      <c r="D306" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr" s="2">
+      <c r="E306" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr" s="3">
+      <c r="F306" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H299"/>
+  <autoFilter ref="A1:H306"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
@@ -262,7 +262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -8896,7 +8896,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -8921,14 +8921,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
+          <t xml:space="preserve">……負けた。…でも、悪くない</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8938,29 +8938,29 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
+          <t xml:space="preserve">……完璧に近かった</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8970,29 +8970,29 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
+          <t xml:space="preserve">GL-01.loss.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
+          <t xml:space="preserve">……足りなかった</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9002,29 +9002,29 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">GL-01.win.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
+          <t xml:space="preserve">……悪くない</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9034,29 +9034,29 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
+          <t xml:space="preserve">GL-02.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
+          <t xml:space="preserve">……（黙々と続けている）</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9066,29 +9066,29 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.quiet[1]</t>
+          <t xml:space="preserve">GL-03.up.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
+          <t xml:space="preserve">……居心地がいい</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9098,29 +9098,29 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.composed.quiet[2]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
+          <t xml:space="preserve">……戻った。…でも何かを掴んだ</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[1]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9145,14 +9145,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
+          <t xml:space="preserve">……ここまで来た。降りる理由がない</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.composed.quiet[2]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9177,14 +9177,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
+          <t xml:space="preserve">……最後の一戦。…立って、迎える</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.quiet[1]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
@@ -9209,14 +9209,14 @@
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
+          <t xml:space="preserve">……誰が来ても、退かない。それだけ</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.composed.quiet[2]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
@@ -9241,14 +9241,14 @@
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
+          <t xml:space="preserve">……焦らない。目の前から、片づける</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
+          <t xml:space="preserve">survivor.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9273,14 +9273,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
+          <t xml:space="preserve">……一人、片づけた。まだ立ってる。……次、来なよ</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
+          <t xml:space="preserve">survivor.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9305,14 +9305,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
+          <t xml:space="preserve">……このリングは渡さない。次は、誰</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……優勝。…ありがとう</t>
+          <t xml:space="preserve">……三人で勝った。それが、今日の全て</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9354,12 +9354,12 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9369,14 +9369,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……一人ではたどり着けなかった場所。仲間が連れてきてくれた</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
+          <t xml:space="preserve">defiant.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9401,14 +9401,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次</t>
+          <t xml:space="preserve">……足りなかった。その事実だけが残る</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.composed.quiet[1]</t>
+          <t xml:space="preserve">defiant.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9433,14 +9433,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪くなかった</t>
+          <t xml:space="preserve">……次は、全てを持って帰る。それだけ</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9465,14 +9465,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……最後。…行くよ</t>
+          <t xml:space="preserve">……何人倒したか。数えるまでもない。立っている、それが答え</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.composed.quiet[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
+          <t xml:space="preserve">gauntlet.composed.quiet[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9497,14 +9497,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……行くよ</t>
+          <t xml:space="preserve">……身体が動く限り、このリングは譲れなかった</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.composed.quiet[1]</t>
+          <t xml:space="preserve">champion.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9529,14 +9529,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……了解</t>
+          <t xml:space="preserve">……優勝。…ありがとう</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9546,12 +9546,12 @@
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">postLose.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9561,14 +9561,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……（静かに構える）</t>
+          <t xml:space="preserve">……次は、負けない</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">postMatchWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9593,14 +9593,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
+          <t xml:space="preserve">……次</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">postWin.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9625,14 +9625,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……対抗戦を。…よろしく</t>
+          <t xml:space="preserve">……悪くなかった</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">composed.quiet[1]</t>
+          <t xml:space="preserve">preFinal.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9657,14 +9657,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……そう</t>
+          <t xml:space="preserve">……最後。…行くよ</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
+          <t xml:space="preserve">preMatch.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9689,14 +9689,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、負けない</t>
+          <t xml:space="preserve">……行くよ</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9706,12 +9706,12 @@
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.composed.quiet[1]</t>
+          <t xml:space="preserve">summon.composed.quiet[1]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9721,14 +9721,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…うん</t>
+          <t xml:space="preserve">……了解</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D296" t="inlineStr" s="12">
@@ -9753,14 +9753,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……勝った。…それだけ</t>
+          <t xml:space="preserve">……（静かに構える）</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9770,29 +9770,29 @@
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+          <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+          <t xml:space="preserve">………（静かにベルトを見つめている）</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.composed.quiet[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D298" t="inlineStr" s="12">
@@ -9812,49 +9812,241 @@
       </c>
       <c r="E298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+          <t xml:space="preserve">……対抗戦を。…よろしく</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……そう</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="40" customHeight="1">
+      <c r="A300" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_lose.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、負けない</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="40" customHeight="1">
+      <c r="A301" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">result_win.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…うん</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="40" customHeight="1">
+      <c r="A302" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。…それだけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="40" customHeight="1">
+      <c r="A303" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ここまで来た。…ありがとう</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="40" customHeight="1">
+      <c r="A304" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">composed.quiet[1]</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……帰る場所ができた。助かるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="40" customHeight="1">
+      <c r="A305" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.composed.quiet[1]</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr" s="2">
+      <c r="B305" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr" s="12">
+      <c r="D305" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">composed.quiet[1]</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr" s="2">
+      <c r="E305" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr" s="3">
+      <c r="F305" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……声がかかった。…なら、やるよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H299"/>
+  <autoFilter ref="A1:H305"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
+++ b/セリフ編集/キャラタイプ別/鷹揚×寡黙.xlsx
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人と、やりたいです。</t>
+          <t xml:space="preserve">社長。…三人で、あちらへ行きたいです。</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…お願いが、ひとつだけ。あの人と、やらせてください。</t>
+          <t xml:space="preserve">…お願いが、ひとつだけ。三人で、行かせてください。</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長。…あの人です。お願いします。</t>
+          <t xml:space="preserve">社長。…あの団体です。三人で、お願いします。</t>
         </is>
       </c>
     </row>
